--- a/Templates/bulkImport/config/construct_RR_config_sslr.xlsx
+++ b/Templates/bulkImport/config/construct_RR_config_sslr.xlsx
@@ -4,56 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="9024"/>
   </bookViews>
   <sheets>
     <sheet name="RR_config_sarawak" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="P5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Times New Roman"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
   <si>
     <t>*</t>
   </si>
@@ -61,6 +22,9 @@
     <t>show</t>
   </si>
   <si>
+    <t>Show</t>
+  </si>
+  <si>
     <t>c_risk_category</t>
   </si>
   <si>
@@ -112,53 +76,13 @@
     <t>c_bulk_import_status</t>
   </si>
   <si>
-    <t>c_close_remarks</t>
-  </si>
-  <si>
-    <t>c_close_attachment</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Risk Category </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
+    <t>Risk Category</t>
   </si>
   <si>
     <t>Risk Event</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Risk Description </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
+    <t>Risk Description</t>
   </si>
   <si>
     <t>Probablility</t>
@@ -173,24 +97,7 @@
     <t>Mitigation</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Percentage Risk Driver </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
+    <t>Percentage Risk Driver</t>
   </si>
   <si>
     <t>Risk Score</t>
@@ -218,25 +125,19 @@
   </si>
   <si>
     <t>Status</t>
-  </si>
-  <si>
-    <t>Close Remarks</t>
-  </si>
-  <si>
-    <t>Close Attachment(s)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -393,19 +294,6 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1208,32 +1096,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S5"/>
-  <sheetFormatPr defaultColWidth="10.287037037037" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A1:Q5"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="14.712962962963" customWidth="1"/>
-    <col min="2" max="2" width="12.1388888888889" customWidth="1"/>
-    <col min="3" max="3" width="17.287037037037" customWidth="1"/>
-    <col min="4" max="4" width="12.5740740740741" customWidth="1"/>
-    <col min="5" max="5" width="7.13888888888889" customWidth="1"/>
-    <col min="6" max="6" width="8.85185185185185" customWidth="1"/>
-    <col min="7" max="7" width="21.1388888888889" customWidth="1"/>
-    <col min="8" max="8" width="22.8518518518519" customWidth="1"/>
-    <col min="9" max="9" width="10.8518518518519" customWidth="1"/>
-    <col min="10" max="10" width="10.5740740740741" customWidth="1"/>
-    <col min="11" max="11" width="13.4259259259259" customWidth="1"/>
-    <col min="12" max="12" width="17.4259259259259" customWidth="1"/>
-    <col min="13" max="13" width="20.4259259259259" customWidth="1"/>
-    <col min="14" max="14" width="8.28703703703704" customWidth="1"/>
-    <col min="15" max="15" width="10.1388888888889" customWidth="1"/>
-    <col min="16" max="16" width="13.4259259259259" customWidth="1"/>
-    <col min="17" max="17" width="8.13888888888889" customWidth="1"/>
+    <col min="1" max="1" width="14.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="12.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="17.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="12.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="7.11111111111111" customWidth="1"/>
+    <col min="6" max="6" width="8.88888888888889" customWidth="1"/>
+    <col min="7" max="8" width="21.1111111111111" customWidth="1"/>
+    <col min="9" max="9" width="10.8888888888889" customWidth="1"/>
+    <col min="10" max="10" width="10.5555555555556" customWidth="1"/>
+    <col min="11" max="11" width="13.4444444444444" customWidth="1"/>
+    <col min="12" max="12" width="17.4444444444444" customWidth="1"/>
+    <col min="13" max="13" width="20.4444444444444" customWidth="1"/>
+    <col min="14" max="14" width="8.33333333333333" customWidth="1"/>
+    <col min="15" max="15" width="10.1111111111111" customWidth="1"/>
+    <col min="16" max="16" width="13.4444444444444" customWidth="1"/>
+    <col min="17" max="17" width="8.11111111111111" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1"/>
       <c r="C1" t="s">
         <v>0</v>
       </c>
@@ -1241,7 +1129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1249,58 +1137,49 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1352,129 +1231,111 @@
       <c r="Q3">
         <v>16</v>
       </c>
-      <c r="R3">
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" t="s">
         <v>17</v>
       </c>
-      <c r="S3">
+      <c r="P4" t="s">
         <v>18</v>
       </c>
+      <c r="Q4" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="4" spans="1:19">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N4" t="s">
-        <v>15</v>
-      </c>
-      <c r="O4" t="s">
-        <v>16</v>
-      </c>
-      <c r="P4" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>18</v>
-      </c>
-      <c r="R4" t="s">
-        <v>19</v>
-      </c>
-      <c r="S4" t="s">
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:19">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>25</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>26</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>27</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>28</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>29</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>30</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>31</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>32</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>33</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>34</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>35</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>36</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>37</v>
-      </c>
-      <c r="R5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S5" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1482,6 +1343,5 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Templates/bulkImport/config/construct_RR_config_sslr.xlsx
+++ b/Templates/bulkImport/config/construct_RR_config_sslr.xlsx
@@ -4,17 +4,56 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9024"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="RR_config_sarawak" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="P5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
   <si>
     <t>*</t>
   </si>
@@ -22,9 +61,6 @@
     <t>show</t>
   </si>
   <si>
-    <t>Show</t>
-  </si>
-  <si>
     <t>c_risk_category</t>
   </si>
   <si>
@@ -76,13 +112,53 @@
     <t>c_bulk_import_status</t>
   </si>
   <si>
-    <t>Risk Category</t>
+    <t>c_close_remarks</t>
+  </si>
+  <si>
+    <t>c_close_attachment</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Risk Category </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
   </si>
   <si>
     <t>Risk Event</t>
   </si>
   <si>
-    <t>Risk Description</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Risk Description </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
   </si>
   <si>
     <t>Probablility</t>
@@ -97,7 +173,24 @@
     <t>Mitigation</t>
   </si>
   <si>
-    <t>Percentage Risk Driver</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Percentage Risk Driver </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
   </si>
   <si>
     <t>Risk Score</t>
@@ -125,19 +218,25 @@
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>Close Remarks</t>
+  </si>
+  <si>
+    <t>Close Attachment(s)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -294,6 +393,19 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1096,32 +1208,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q5"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultColWidth="10.287037037037" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="14.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="12.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="17.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="12.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="7.11111111111111" customWidth="1"/>
-    <col min="6" max="6" width="8.88888888888889" customWidth="1"/>
-    <col min="7" max="8" width="21.1111111111111" customWidth="1"/>
-    <col min="9" max="9" width="10.8888888888889" customWidth="1"/>
-    <col min="10" max="10" width="10.5555555555556" customWidth="1"/>
-    <col min="11" max="11" width="13.4444444444444" customWidth="1"/>
-    <col min="12" max="12" width="17.4444444444444" customWidth="1"/>
-    <col min="13" max="13" width="20.4444444444444" customWidth="1"/>
-    <col min="14" max="14" width="8.33333333333333" customWidth="1"/>
-    <col min="15" max="15" width="10.1111111111111" customWidth="1"/>
-    <col min="16" max="16" width="13.4444444444444" customWidth="1"/>
-    <col min="17" max="17" width="8.11111111111111" customWidth="1"/>
+    <col min="1" max="1" width="14.712962962963" customWidth="1"/>
+    <col min="2" max="2" width="12.1388888888889" customWidth="1"/>
+    <col min="3" max="3" width="17.287037037037" customWidth="1"/>
+    <col min="4" max="4" width="12.5740740740741" customWidth="1"/>
+    <col min="5" max="5" width="7.13888888888889" customWidth="1"/>
+    <col min="6" max="6" width="8.85185185185185" customWidth="1"/>
+    <col min="7" max="7" width="21.1388888888889" customWidth="1"/>
+    <col min="8" max="8" width="22.8518518518519" customWidth="1"/>
+    <col min="9" max="9" width="10.8518518518519" customWidth="1"/>
+    <col min="10" max="10" width="10.5740740740741" customWidth="1"/>
+    <col min="11" max="11" width="13.4259259259259" customWidth="1"/>
+    <col min="12" max="12" width="17.4259259259259" customWidth="1"/>
+    <col min="13" max="13" width="20.4259259259259" customWidth="1"/>
+    <col min="14" max="14" width="8.28703703703704" customWidth="1"/>
+    <col min="15" max="15" width="10.1388888888889" customWidth="1"/>
+    <col min="16" max="16" width="13.4259259259259" customWidth="1"/>
+    <col min="17" max="17" width="8.13888888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1"/>
       <c r="C1" t="s">
         <v>0</v>
       </c>
@@ -1129,7 +1241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1137,49 +1249,58 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="R2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1231,111 +1352,129 @@
       <c r="Q3">
         <v>16</v>
       </c>
+      <c r="R3">
+        <v>17</v>
+      </c>
+      <c r="S3">
+        <v>18</v>
+      </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:19">
       <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>7</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>8</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>9</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>10</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>11</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>12</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>13</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>14</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>15</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>16</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>17</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>18</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>19</v>
       </c>
+      <c r="S4" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q5" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S5" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1343,5 +1482,6 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>